--- a/test-results/e2e-modality/Q4_Model.xlsx
+++ b/test-results/e2e-modality/Q4_Model.xlsx
@@ -592,6 +592,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E4"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" errorTitle="Invalid value" error="Pick a listed value" sqref="B2:B4">
       <formula1>"NA,EMEA,APAC"</formula1>
@@ -642,6 +643,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
